--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.12173770201797</v>
+        <v>3.75728237657792</v>
       </c>
       <c r="D2" t="n">
-        <v>27.85344584158451</v>
+        <v>4.526184949257482</v>
       </c>
       <c r="E2" t="n">
-        <v>12.41465647286339</v>
+        <v>2.017381676840301</v>
       </c>
       <c r="F2" t="n">
-        <v>10.6351341486572</v>
+        <v>1.728209299156795</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.95105064774475</v>
+        <v>7.792045730258522</v>
       </c>
       <c r="D3" t="n">
-        <v>49.1237141388989</v>
+        <v>7.982603547571072</v>
       </c>
       <c r="E3" t="n">
-        <v>12.41465647286339</v>
+        <v>2.017381676840301</v>
       </c>
       <c r="F3" t="n">
-        <v>10.6351341486572</v>
+        <v>1.728209299156795</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
